--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.422</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.706</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.43</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>4.056</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.922</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.443</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1229"/>
+  <dimension ref="A1:J1230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42271,6 +42271,40 @@
         <v>0.443</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1230" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="D1230" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E1230" s="3" t="n">
+        <v>4.713</v>
+      </c>
+      <c r="F1230" s="3" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="G1230" s="3" t="n">
+        <v>3.922</v>
+      </c>
+      <c r="H1230" s="3" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="I1230" s="3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J1230" s="3" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.498</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>4.076</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.755</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.528</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>4.011</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.703</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>4.077</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.539</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.5659999999999999</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.937</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.638</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.638</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.576</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.576</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.576</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.636</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.574</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.574</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.961</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.644</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.994</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.572</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.983</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.651</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.985</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.574</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.574</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.921</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.602</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.602</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.949</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.558</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.5580000000000001</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.537</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.537</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.883</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.54</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.541</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.543</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.5580000000000001</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.534</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.941</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.5679999999999999</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.803</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.547</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.758</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.447</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.942</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.526</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.526</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.954</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.535</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.939</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.518</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.518</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.924</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.484</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
